--- a/overview.xlsx
+++ b/overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vinmas/repositories/os_material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1222419-DE57-3349-B4A2-B90B4206F08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A6B1D4-F334-CE4C-AD96-AE0359B90184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="660" windowWidth="28040" windowHeight="17020" xr2:uid="{67D7C5C9-BFD9-9043-B236-4D7F530C133A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="116">
   <si>
     <t>Lecture</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>should check cutting in the beginning If we are no longer pointing to Silberschatz, those instructions should go from the slides</t>
+  </si>
+  <si>
+    <t>If we are no longer pointing to Silberschatz, those instructions should go from the slides. Also, important update on slide 7, should re-make the video!</t>
+  </si>
+  <si>
+    <t>This video is to be redone too (priority)</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1352,7 @@
         <v>14</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1425,6 +1431,9 @@
       </c>
       <c r="H24" t="s">
         <v>14</v>
+      </c>
+      <c r="I24" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vinmas/repositories/os_material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A6B1D4-F334-CE4C-AD96-AE0359B90184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEDEB2F-FDD1-C348-B4E5-FB307DA68091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="660" windowWidth="28040" windowHeight="17020" xr2:uid="{67D7C5C9-BFD9-9043-B236-4D7F530C133A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="118">
   <si>
     <t>Lecture</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>This video is to be redone too (priority)</t>
+  </si>
+  <si>
+    <t>Conceptual error in example, needs to be re-recorded!</t>
+  </si>
+  <si>
+    <t>Some slides changed, should re-record</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,6 +431,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,12 +453,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1646,6 +1659,9 @@
       <c r="H32" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="I32" s="5" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -1698,7 +1714,9 @@
       <c r="H34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">

--- a/overview.xlsx
+++ b/overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vinmas/repositories/os_material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEDEB2F-FDD1-C348-B4E5-FB307DA68091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB68EAB-9D43-D341-A96A-092047CC0CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="660" windowWidth="28040" windowHeight="17020" xr2:uid="{67D7C5C9-BFD9-9043-B236-4D7F530C133A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="121">
   <si>
     <t>Lecture</t>
   </si>
@@ -393,6 +393,15 @@
   </si>
   <si>
     <t>Some slides changed, should re-record</t>
+  </si>
+  <si>
+    <t>Should duplicate pseudocodes to show both A and B where needed</t>
+  </si>
+  <si>
+    <t>remake video (Updated def of no preemption)</t>
+  </si>
+  <si>
+    <t>there was a mistake in the explanation, should redo video</t>
   </si>
 </sst>
 </file>
@@ -794,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F787F616-B8B6-AD4D-913E-A16EDA262922}">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -1235,7 +1244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
@@ -1339,7 +1348,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1368,7 +1377,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1394,7 +1403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1420,7 +1429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1449,7 +1458,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -1475,7 +1484,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1501,7 +1510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -1555,8 +1564,11 @@
       <c r="I28" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J28" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
@@ -1581,8 +1593,11 @@
       <c r="H29" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J29" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
@@ -1607,8 +1622,11 @@
       <c r="H30" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J30" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
@@ -1633,8 +1651,11 @@
       <c r="H31" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J31" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1662,8 +1683,11 @@
       <c r="I32" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J32" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
@@ -1688,8 +1712,11 @@
       <c r="H33" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J33" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -1717,8 +1744,11 @@
       <c r="I34" s="5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J34" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>22</v>
       </c>
@@ -1746,8 +1776,9 @@
       <c r="I35" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>22</v>
       </c>
@@ -1772,8 +1803,11 @@
       <c r="H36" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J36" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>22</v>
       </c>
@@ -1798,8 +1832,9 @@
       <c r="H37" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>22</v>
       </c>
@@ -1824,8 +1859,11 @@
       <c r="H38" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J38" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>22</v>
       </c>
@@ -1850,8 +1888,9 @@
       <c r="H39" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
@@ -1876,8 +1915,9 @@
       <c r="H40" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
@@ -1902,8 +1942,9 @@
       <c r="H41" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
@@ -1928,8 +1969,9 @@
       <c r="H42" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -1957,8 +1999,9 @@
       <c r="I43" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>24</v>
       </c>
@@ -1987,7 +2030,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
@@ -2016,7 +2059,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -2045,7 +2088,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
@@ -2074,7 +2117,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
